--- a/automation/reports/Excel/Unit_Test_Cases.xlsx
+++ b/automation/reports/Excel/Unit_Test_Cases.xlsx
@@ -468,7 +468,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #1</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0055</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #2</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #3</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #4</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #5</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #6</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #7</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #8</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #9</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #10</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #11</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #12</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #13</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #14</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #15</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #16</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #17</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #18</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #19</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #20</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #21</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #22</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #23</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #24</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #25</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #26</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #27</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #28</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #29</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #30</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #31</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #32</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #33</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #34</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #35</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #36</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #37</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #38</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #39</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #40</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #41</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #42</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #43</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #44</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #45</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #46</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #47</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #48</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #49</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #50</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #51</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #52</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #53</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #54</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #55</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #56</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #57</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #58</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #59</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #60</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #61</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #62</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #63</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #64</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #65</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #66</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #67</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #68</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #69</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #70</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #71</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #72</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #73</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #74</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #75</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #76</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #77</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #78</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #79</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #80</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #81</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #82</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #83</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #84</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #85</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #86</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #87</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #88</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #89</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #90</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #91</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #92</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #93</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #94</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #95</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #96</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #97</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #98</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #99</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #100</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #101</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #102</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #103</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #104</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #105</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #106</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #107</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #108</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #109</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #110</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #111</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #112</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #113</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #114</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #115</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #116</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #117</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #118</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #119</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #120</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #121</t>
+          <t>Verify backend system configuration parameters for setting index 1</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #122</t>
+          <t>Verify backend system configuration parameters for setting index 2</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #123</t>
+          <t>Verify backend system configuration parameters for setting index 3</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #124</t>
+          <t>Verify backend system configuration parameters for setting index 4</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #125</t>
+          <t>Verify backend system configuration parameters for setting index 5</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #126</t>
+          <t>Verify backend system configuration parameters for setting index 6</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #127</t>
+          <t>Verify backend system configuration parameters for setting index 7</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #128</t>
+          <t>Verify backend system configuration parameters for setting index 8</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #129</t>
+          <t>Verify backend system configuration parameters for setting index 9</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #130</t>
+          <t>Verify backend system configuration parameters for setting index 10</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #131</t>
+          <t>Verify backend system configuration parameters for setting index 11</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #132</t>
+          <t>Verify backend system configuration parameters for setting index 12</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #133</t>
+          <t>Verify backend system configuration parameters for setting index 13</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #134</t>
+          <t>Verify backend system configuration parameters for setting index 14</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #135</t>
+          <t>Verify backend system configuration parameters for setting index 15</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #136</t>
+          <t>Verify backend system configuration parameters for setting index 16</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #137</t>
+          <t>Verify backend system configuration parameters for setting index 17</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #138</t>
+          <t>Verify backend system configuration parameters for setting index 18</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #139</t>
+          <t>Verify backend system configuration parameters for setting index 19</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #140</t>
+          <t>Verify backend system configuration parameters for setting index 20</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #141</t>
+          <t>Verify backend system configuration parameters for setting index 21</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #142</t>
+          <t>Verify backend system configuration parameters for setting index 22</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #143</t>
+          <t>Verify backend system configuration parameters for setting index 23</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #144</t>
+          <t>Verify backend system configuration parameters for setting index 24</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #145</t>
+          <t>Verify backend system configuration parameters for setting index 25</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #146</t>
+          <t>Verify backend system configuration parameters for setting index 26</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #147</t>
+          <t>Verify backend system configuration parameters for setting index 27</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #148</t>
+          <t>Verify backend system configuration parameters for setting index 28</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #149</t>
+          <t>Verify backend system configuration parameters for setting index 29</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #150</t>
+          <t>Verify backend system configuration parameters for setting index 30</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #151</t>
+          <t>Verify backend system configuration parameters for setting index 31</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #152</t>
+          <t>Verify backend system configuration parameters for setting index 32</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #153</t>
+          <t>Verify backend system configuration parameters for setting index 33</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #154</t>
+          <t>Verify backend system configuration parameters for setting index 34</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #155</t>
+          <t>Verify backend system configuration parameters for setting index 35</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #156</t>
+          <t>Verify backend system configuration parameters for setting index 36</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #157</t>
+          <t>Verify backend system configuration parameters for setting index 37</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #158</t>
+          <t>Verify backend system configuration parameters for setting index 38</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #159</t>
+          <t>Verify backend system configuration parameters for setting index 39</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #160</t>
+          <t>Verify backend system configuration parameters for setting index 40</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #161</t>
+          <t>Verify backend system configuration parameters for setting index 41</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #162</t>
+          <t>Verify backend system configuration parameters for setting index 42</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #163</t>
+          <t>Verify backend system configuration parameters for setting index 43</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #164</t>
+          <t>Verify backend system configuration parameters for setting index 44</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #165</t>
+          <t>Verify backend system configuration parameters for setting index 45</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #166</t>
+          <t>Verify backend system configuration parameters for setting index 46</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #167</t>
+          <t>Verify backend system configuration parameters for setting index 47</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #168</t>
+          <t>Verify backend system configuration parameters for setting index 48</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #169</t>
+          <t>Verify backend system configuration parameters for setting index 49</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #170</t>
+          <t>Verify backend system configuration parameters for setting index 50</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #171</t>
+          <t>Verify backend system configuration parameters for setting index 51</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #172</t>
+          <t>Verify backend system configuration parameters for setting index 52</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #173</t>
+          <t>Verify backend system configuration parameters for setting index 53</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #174</t>
+          <t>Verify backend system configuration parameters for setting index 54</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #175</t>
+          <t>Verify backend system configuration parameters for setting index 55</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -6629,7 +6629,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #176</t>
+          <t>Verify backend system configuration parameters for setting index 56</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #177</t>
+          <t>Verify backend system configuration parameters for setting index 57</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #178</t>
+          <t>Verify backend system configuration parameters for setting index 58</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #179</t>
+          <t>Verify backend system configuration parameters for setting index 59</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #180</t>
+          <t>Verify backend system configuration parameters for setting index 60</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #181</t>
+          <t>Subtract wrist origin coordinates (1.81, 3.62) during landmark normalization</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #182</t>
+          <t>Subtract wrist origin coordinates (1.82, 3.64) during landmark normalization</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #183</t>
+          <t>Subtract wrist origin coordinates (1.83, 3.66) during landmark normalization</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #184</t>
+          <t>Subtract wrist origin coordinates (1.84, 3.68) during landmark normalization</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #185</t>
+          <t>Subtract wrist origin coordinates (1.85, 3.7) during landmark normalization</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (1.85, 3.70) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (1.85, 3.7) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #186</t>
+          <t>Subtract wrist origin coordinates (1.86, 3.72) during landmark normalization</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #187</t>
+          <t>Subtract wrist origin coordinates (1.87, 3.74) during landmark normalization</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #188</t>
+          <t>Subtract wrist origin coordinates (1.88, 3.76) during landmark normalization</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #189</t>
+          <t>Subtract wrist origin coordinates (1.89, 3.78) during landmark normalization</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #190</t>
+          <t>Subtract wrist origin coordinates (1.9, 3.8) during landmark normalization</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (1.90, 3.80) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (1.9, 3.8) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #191</t>
+          <t>Subtract wrist origin coordinates (1.91, 3.82) during landmark normalization</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #192</t>
+          <t>Subtract wrist origin coordinates (1.92, 3.84) during landmark normalization</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #193</t>
+          <t>Subtract wrist origin coordinates (1.93, 3.86) during landmark normalization</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #194</t>
+          <t>Subtract wrist origin coordinates (1.94, 3.88) during landmark normalization</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #195</t>
+          <t>Subtract wrist origin coordinates (1.95, 3.9) during landmark normalization</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (1.95, 3.90) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (1.95, 3.9) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #196</t>
+          <t>Subtract wrist origin coordinates (1.96, 3.92) during landmark normalization</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #197</t>
+          <t>Subtract wrist origin coordinates (1.97, 3.94) during landmark normalization</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #198</t>
+          <t>Subtract wrist origin coordinates (1.98, 3.96) during landmark normalization</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #199</t>
+          <t>Subtract wrist origin coordinates (1.99, 3.98) during landmark normalization</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #200</t>
+          <t>Subtract wrist origin coordinates (2.0, 4.0) during landmark normalization</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.00, 4.00) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.0, 4.0) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #201</t>
+          <t>Subtract wrist origin coordinates (2.01, 4.02) during landmark normalization</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #202</t>
+          <t>Subtract wrist origin coordinates (2.02, 4.04) during landmark normalization</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #203</t>
+          <t>Subtract wrist origin coordinates (2.03, 4.06) during landmark normalization</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #204</t>
+          <t>Subtract wrist origin coordinates (2.04, 4.08) during landmark normalization</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #205</t>
+          <t>Subtract wrist origin coordinates (2.05, 4.1) during landmark normalization</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.05, 4.10) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.05, 4.1) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #206</t>
+          <t>Subtract wrist origin coordinates (2.06, 4.12) during landmark normalization</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #207</t>
+          <t>Subtract wrist origin coordinates (2.07, 4.14) during landmark normalization</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #208</t>
+          <t>Subtract wrist origin coordinates (2.08, 4.16) during landmark normalization</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #209</t>
+          <t>Subtract wrist origin coordinates (2.09, 4.18) during landmark normalization</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #210</t>
+          <t>Subtract wrist origin coordinates (2.1, 4.2) during landmark normalization</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.10, 4.20) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.1, 4.2) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #211</t>
+          <t>Subtract wrist origin coordinates (2.11, 4.22) during landmark normalization</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #212</t>
+          <t>Subtract wrist origin coordinates (2.12, 4.24) during landmark normalization</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #213</t>
+          <t>Subtract wrist origin coordinates (2.13, 4.26) during landmark normalization</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #214</t>
+          <t>Subtract wrist origin coordinates (2.14, 4.28) during landmark normalization</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #215</t>
+          <t>Subtract wrist origin coordinates (2.15, 4.3) during landmark normalization</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.15, 4.30) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.15, 4.3) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #216</t>
+          <t>Subtract wrist origin coordinates (2.16, 4.32) during landmark normalization</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #217</t>
+          <t>Subtract wrist origin coordinates (2.17, 4.34) during landmark normalization</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #218</t>
+          <t>Subtract wrist origin coordinates (2.18, 4.36) during landmark normalization</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #219</t>
+          <t>Subtract wrist origin coordinates (2.19, 4.38) during landmark normalization</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #220</t>
+          <t>Subtract wrist origin coordinates (2.2, 4.4) during landmark normalization</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.20, 4.40) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.2, 4.4) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #221</t>
+          <t>Subtract wrist origin coordinates (2.21, 4.42) during landmark normalization</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #222</t>
+          <t>Subtract wrist origin coordinates (2.22, 4.44) during landmark normalization</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #223</t>
+          <t>Subtract wrist origin coordinates (2.23, 4.46) during landmark normalization</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #224</t>
+          <t>Subtract wrist origin coordinates (2.24, 4.48) during landmark normalization</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #225</t>
+          <t>Subtract wrist origin coordinates (2.25, 4.5) during landmark normalization</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.25, 4.50) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.25, 4.5) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #226</t>
+          <t>Subtract wrist origin coordinates (2.26, 4.52) during landmark normalization</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #227</t>
+          <t>Subtract wrist origin coordinates (2.27, 4.54) during landmark normalization</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #228</t>
+          <t>Subtract wrist origin coordinates (2.28, 4.56) during landmark normalization</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #229</t>
+          <t>Subtract wrist origin coordinates (2.29, 4.58) during landmark normalization</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #230</t>
+          <t>Subtract wrist origin coordinates (2.3, 4.6) during landmark normalization</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.30, 4.60) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.3, 4.6) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #231</t>
+          <t>Subtract wrist origin coordinates (2.31, 4.62) during landmark normalization</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #232</t>
+          <t>Subtract wrist origin coordinates (2.32, 4.64) during landmark normalization</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #233</t>
+          <t>Subtract wrist origin coordinates (2.33, 4.66) during landmark normalization</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #234</t>
+          <t>Subtract wrist origin coordinates (2.34, 4.68) during landmark normalization</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #235</t>
+          <t>Subtract wrist origin coordinates (2.35, 4.7) during landmark normalization</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.35, 4.70) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.35, 4.7) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #236</t>
+          <t>Subtract wrist origin coordinates (2.36, 4.72) during landmark normalization</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #237</t>
+          <t>Subtract wrist origin coordinates (2.37, 4.74) during landmark normalization</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #238</t>
+          <t>Subtract wrist origin coordinates (2.38, 4.76) during landmark normalization</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #239</t>
+          <t>Subtract wrist origin coordinates (2.39, 4.78) during landmark normalization</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #240</t>
+          <t>Subtract wrist origin coordinates (2.4, 4.8) during landmark normalization</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.40, 4.80) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.4, 4.8) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #241</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 1</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #242</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 2</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #243</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 3</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #244</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 4</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #245</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 5</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #246</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 6</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #247</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 7</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #248</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 8</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #249</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 9</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #250</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 10</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #251</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 11</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #252</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 12</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #253</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 13</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #254</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 14</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="F255" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #255</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 15</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #256</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 16</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #257</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 17</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #258</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 18</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #259</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 19</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #260</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 20</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #261</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 21</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #262</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 22</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #263</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 23</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #264</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 24</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #265</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 25</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #266</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 26</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -9814,7 +9814,7 @@
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #267</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 27</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #268</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 28</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #269</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 29</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -9919,7 +9919,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #270</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 30</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #271</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 31</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #272</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 32</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #273</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 33</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #274</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 34</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #275</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 35</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #276</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 36</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #277</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 37</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #278</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 38</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #279</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 39</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -10269,7 +10269,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #280</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 40</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #281</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 41</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #282</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 42</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #283</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 43</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #284</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 44</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #285</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 45</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #286</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 46</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #287</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 47</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #288</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 48</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -10584,7 +10584,7 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #289</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 49</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #290</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 50</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #291</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 51</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -10689,7 +10689,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #292</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 52</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #293</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 53</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #294</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 54</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #295</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 55</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #296</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 56</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #297</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 57</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #298</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 58</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #299</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 59</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -10969,7 +10969,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #300</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 60</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #1</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11099,7 +11099,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0055</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #2</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #3</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #4</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #5</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #6</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #7</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #8</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #9</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #10</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #11</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #12</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #13</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #14</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #15</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #16</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #17</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #18</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #19</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #20</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #21</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #22</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #23</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #24</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #25</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #26</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #27</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #28</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #29</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #30</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #31</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #32</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #33</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #34</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #35</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #36</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #37</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #38</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #39</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #40</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #41</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #42</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #43</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #44</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #45</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #46</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #47</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #48</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #49</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #50</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #51</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #52</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #53</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #54</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #55</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #56</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.1</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #57</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.2</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #58</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.3</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #59</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.4</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Landmark coordinate vector normalization #60</t>
+          <t>Normalize 21 hand landmark coordinates for coordinate scale 0.0</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #61</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #62</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #63</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #64</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #65</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #66</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #67</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #68</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #69</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #70</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #71</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #72</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #73</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #74</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #75</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #76</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #77</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #78</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #79</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #80</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #81</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #82</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #83</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #84</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #85</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #86</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -14074,7 +14074,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #87</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #88</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #89</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #90</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #91</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #92</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #93</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #94</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #95</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #96</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #97</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #98</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #99</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #100</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #101</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #102</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #103</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #104</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #105</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #106</t>
+          <t>Pad temporal landmark sequence containing 2 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #107</t>
+          <t>Pad temporal landmark sequence containing 3 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #108</t>
+          <t>Pad temporal landmark sequence containing 4 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #109</t>
+          <t>Pad temporal landmark sequence containing 5 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #110</t>
+          <t>Pad temporal landmark sequence containing 6 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #111</t>
+          <t>Pad temporal landmark sequence containing 7 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #112</t>
+          <t>Pad temporal landmark sequence containing 8 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #113</t>
+          <t>Pad temporal landmark sequence containing 9 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #114</t>
+          <t>Pad temporal landmark sequence containing 10 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #115</t>
+          <t>Pad temporal landmark sequence containing 11 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #116</t>
+          <t>Pad temporal landmark sequence containing 12 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -15124,7 +15124,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #117</t>
+          <t>Pad temporal landmark sequence containing 13 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -15159,7 +15159,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #118</t>
+          <t>Pad temporal landmark sequence containing 14 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #119</t>
+          <t>Pad temporal landmark sequence containing 15 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Temporal landmark sequence padding #120</t>
+          <t>Pad temporal landmark sequence containing 1 frames to fixed length 15</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #121</t>
+          <t>Verify backend system configuration parameters for setting index 1</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #122</t>
+          <t>Verify backend system configuration parameters for setting index 2</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #123</t>
+          <t>Verify backend system configuration parameters for setting index 3</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #124</t>
+          <t>Verify backend system configuration parameters for setting index 4</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #125</t>
+          <t>Verify backend system configuration parameters for setting index 5</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -15439,7 +15439,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #126</t>
+          <t>Verify backend system configuration parameters for setting index 6</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -15474,7 +15474,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #127</t>
+          <t>Verify backend system configuration parameters for setting index 7</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #128</t>
+          <t>Verify backend system configuration parameters for setting index 8</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #129</t>
+          <t>Verify backend system configuration parameters for setting index 9</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #130</t>
+          <t>Verify backend system configuration parameters for setting index 10</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #131</t>
+          <t>Verify backend system configuration parameters for setting index 11</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #132</t>
+          <t>Verify backend system configuration parameters for setting index 12</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #133</t>
+          <t>Verify backend system configuration parameters for setting index 13</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #134</t>
+          <t>Verify backend system configuration parameters for setting index 14</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #135</t>
+          <t>Verify backend system configuration parameters for setting index 15</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #136</t>
+          <t>Verify backend system configuration parameters for setting index 16</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -15824,7 +15824,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #137</t>
+          <t>Verify backend system configuration parameters for setting index 17</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -15859,7 +15859,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #138</t>
+          <t>Verify backend system configuration parameters for setting index 18</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #139</t>
+          <t>Verify backend system configuration parameters for setting index 19</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #140</t>
+          <t>Verify backend system configuration parameters for setting index 20</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #141</t>
+          <t>Verify backend system configuration parameters for setting index 21</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -15999,7 +15999,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #142</t>
+          <t>Verify backend system configuration parameters for setting index 22</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -16034,7 +16034,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #143</t>
+          <t>Verify backend system configuration parameters for setting index 23</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -16069,7 +16069,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #144</t>
+          <t>Verify backend system configuration parameters for setting index 24</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -16104,7 +16104,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #145</t>
+          <t>Verify backend system configuration parameters for setting index 25</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #146</t>
+          <t>Verify backend system configuration parameters for setting index 26</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -16174,7 +16174,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #147</t>
+          <t>Verify backend system configuration parameters for setting index 27</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #148</t>
+          <t>Verify backend system configuration parameters for setting index 28</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #149</t>
+          <t>Verify backend system configuration parameters for setting index 29</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #150</t>
+          <t>Verify backend system configuration parameters for setting index 30</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #151</t>
+          <t>Verify backend system configuration parameters for setting index 31</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -16349,7 +16349,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #152</t>
+          <t>Verify backend system configuration parameters for setting index 32</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #153</t>
+          <t>Verify backend system configuration parameters for setting index 33</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #154</t>
+          <t>Verify backend system configuration parameters for setting index 34</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -16454,7 +16454,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #155</t>
+          <t>Verify backend system configuration parameters for setting index 35</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -16510,7 +16510,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #156</t>
+          <t>Verify backend system configuration parameters for setting index 36</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -16524,7 +16524,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #157</t>
+          <t>Verify backend system configuration parameters for setting index 37</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #158</t>
+          <t>Verify backend system configuration parameters for setting index 38</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -16594,7 +16594,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #159</t>
+          <t>Verify backend system configuration parameters for setting index 39</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -16629,7 +16629,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #160</t>
+          <t>Verify backend system configuration parameters for setting index 40</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -16664,7 +16664,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #161</t>
+          <t>Verify backend system configuration parameters for setting index 41</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #162</t>
+          <t>Verify backend system configuration parameters for setting index 42</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #163</t>
+          <t>Verify backend system configuration parameters for setting index 43</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #164</t>
+          <t>Verify backend system configuration parameters for setting index 44</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #165</t>
+          <t>Verify backend system configuration parameters for setting index 45</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -16839,7 +16839,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #166</t>
+          <t>Verify backend system configuration parameters for setting index 46</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -16874,7 +16874,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #167</t>
+          <t>Verify backend system configuration parameters for setting index 47</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -16909,7 +16909,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #168</t>
+          <t>Verify backend system configuration parameters for setting index 48</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -16944,7 +16944,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #169</t>
+          <t>Verify backend system configuration parameters for setting index 49</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #170</t>
+          <t>Verify backend system configuration parameters for setting index 50</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #171</t>
+          <t>Verify backend system configuration parameters for setting index 51</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -17049,7 +17049,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #172</t>
+          <t>Verify backend system configuration parameters for setting index 52</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #173</t>
+          <t>Verify backend system configuration parameters for setting index 53</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -17119,7 +17119,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #174</t>
+          <t>Verify backend system configuration parameters for setting index 54</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #175</t>
+          <t>Verify backend system configuration parameters for setting index 55</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -17189,7 +17189,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #176</t>
+          <t>Verify backend system configuration parameters for setting index 56</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -17224,7 +17224,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #177</t>
+          <t>Verify backend system configuration parameters for setting index 57</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #178</t>
+          <t>Verify backend system configuration parameters for setting index 58</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -17294,7 +17294,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #179</t>
+          <t>Verify backend system configuration parameters for setting index 59</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>System configuration setting verification #180</t>
+          <t>Verify backend system configuration parameters for setting index 60</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #181</t>
+          <t>Subtract wrist origin coordinates (1.81, 3.62) during landmark normalization</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #182</t>
+          <t>Subtract wrist origin coordinates (1.82, 3.64) during landmark normalization</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #183</t>
+          <t>Subtract wrist origin coordinates (1.83, 3.66) during landmark normalization</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #184</t>
+          <t>Subtract wrist origin coordinates (1.84, 3.68) during landmark normalization</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #185</t>
+          <t>Subtract wrist origin coordinates (1.85, 3.7) during landmark normalization</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (1.85, 3.70) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (1.85, 3.7) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #186</t>
+          <t>Subtract wrist origin coordinates (1.86, 3.72) during landmark normalization</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #187</t>
+          <t>Subtract wrist origin coordinates (1.87, 3.74) during landmark normalization</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #188</t>
+          <t>Subtract wrist origin coordinates (1.88, 3.76) during landmark normalization</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -17665,7 +17665,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #189</t>
+          <t>Subtract wrist origin coordinates (1.89, 3.78) during landmark normalization</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #190</t>
+          <t>Subtract wrist origin coordinates (1.9, 3.8) during landmark normalization</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (1.90, 3.80) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (1.9, 3.8) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #191</t>
+          <t>Subtract wrist origin coordinates (1.91, 3.82) during landmark normalization</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #192</t>
+          <t>Subtract wrist origin coordinates (1.92, 3.84) during landmark normalization</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #193</t>
+          <t>Subtract wrist origin coordinates (1.93, 3.86) during landmark normalization</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #194</t>
+          <t>Subtract wrist origin coordinates (1.94, 3.88) during landmark normalization</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -17875,7 +17875,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #195</t>
+          <t>Subtract wrist origin coordinates (1.95, 3.9) during landmark normalization</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (1.95, 3.90) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (1.95, 3.9) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #196</t>
+          <t>Subtract wrist origin coordinates (1.96, 3.92) during landmark normalization</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #197</t>
+          <t>Subtract wrist origin coordinates (1.97, 3.94) during landmark normalization</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -17980,7 +17980,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #198</t>
+          <t>Subtract wrist origin coordinates (1.98, 3.96) during landmark normalization</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #199</t>
+          <t>Subtract wrist origin coordinates (1.99, 3.98) during landmark normalization</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #200</t>
+          <t>Subtract wrist origin coordinates (2.0, 4.0) during landmark normalization</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.00, 4.00) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.0, 4.0) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #201</t>
+          <t>Subtract wrist origin coordinates (2.01, 4.02) during landmark normalization</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #202</t>
+          <t>Subtract wrist origin coordinates (2.02, 4.04) during landmark normalization</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #203</t>
+          <t>Subtract wrist origin coordinates (2.03, 4.06) during landmark normalization</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #204</t>
+          <t>Subtract wrist origin coordinates (2.04, 4.08) during landmark normalization</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #205</t>
+          <t>Subtract wrist origin coordinates (2.05, 4.1) during landmark normalization</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.05, 4.10) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.05, 4.1) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18260,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #206</t>
+          <t>Subtract wrist origin coordinates (2.06, 4.12) during landmark normalization</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #207</t>
+          <t>Subtract wrist origin coordinates (2.07, 4.14) during landmark normalization</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #208</t>
+          <t>Subtract wrist origin coordinates (2.08, 4.16) during landmark normalization</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #209</t>
+          <t>Subtract wrist origin coordinates (2.09, 4.18) during landmark normalization</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #210</t>
+          <t>Subtract wrist origin coordinates (2.1, 4.2) during landmark normalization</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.10, 4.20) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.1, 4.2) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #211</t>
+          <t>Subtract wrist origin coordinates (2.11, 4.22) during landmark normalization</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #212</t>
+          <t>Subtract wrist origin coordinates (2.12, 4.24) during landmark normalization</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #213</t>
+          <t>Subtract wrist origin coordinates (2.13, 4.26) during landmark normalization</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -18540,7 +18540,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #214</t>
+          <t>Subtract wrist origin coordinates (2.14, 4.28) during landmark normalization</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #215</t>
+          <t>Subtract wrist origin coordinates (2.15, 4.3) during landmark normalization</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.15, 4.30) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.15, 4.3) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #216</t>
+          <t>Subtract wrist origin coordinates (2.16, 4.32) during landmark normalization</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #217</t>
+          <t>Subtract wrist origin coordinates (2.17, 4.34) during landmark normalization</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #218</t>
+          <t>Subtract wrist origin coordinates (2.18, 4.36) during landmark normalization</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #219</t>
+          <t>Subtract wrist origin coordinates (2.19, 4.38) during landmark normalization</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -18750,7 +18750,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #220</t>
+          <t>Subtract wrist origin coordinates (2.2, 4.4) during landmark normalization</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -18768,7 +18768,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.20, 4.40) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.2, 4.4) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18785,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #221</t>
+          <t>Subtract wrist origin coordinates (2.21, 4.42) during landmark normalization</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #222</t>
+          <t>Subtract wrist origin coordinates (2.22, 4.44) during landmark normalization</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -18855,7 +18855,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #223</t>
+          <t>Subtract wrist origin coordinates (2.23, 4.46) during landmark normalization</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #224</t>
+          <t>Subtract wrist origin coordinates (2.24, 4.48) during landmark normalization</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #225</t>
+          <t>Subtract wrist origin coordinates (2.25, 4.5) during landmark normalization</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.25, 4.50) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.25, 4.5) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #226</t>
+          <t>Subtract wrist origin coordinates (2.26, 4.52) during landmark normalization</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #227</t>
+          <t>Subtract wrist origin coordinates (2.27, 4.54) during landmark normalization</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #228</t>
+          <t>Subtract wrist origin coordinates (2.28, 4.56) during landmark normalization</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -19065,7 +19065,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #229</t>
+          <t>Subtract wrist origin coordinates (2.29, 4.58) during landmark normalization</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #230</t>
+          <t>Subtract wrist origin coordinates (2.3, 4.6) during landmark normalization</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.30, 4.60) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.3, 4.6) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -19135,7 +19135,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #231</t>
+          <t>Subtract wrist origin coordinates (2.31, 4.62) during landmark normalization</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #232</t>
+          <t>Subtract wrist origin coordinates (2.32, 4.64) during landmark normalization</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #233</t>
+          <t>Subtract wrist origin coordinates (2.33, 4.66) during landmark normalization</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #234</t>
+          <t>Subtract wrist origin coordinates (2.34, 4.68) during landmark normalization</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #235</t>
+          <t>Subtract wrist origin coordinates (2.35, 4.7) during landmark normalization</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.35, 4.70) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.35, 4.7) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -19310,7 +19310,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #236</t>
+          <t>Subtract wrist origin coordinates (2.36, 4.72) during landmark normalization</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #237</t>
+          <t>Subtract wrist origin coordinates (2.37, 4.74) during landmark normalization</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #238</t>
+          <t>Subtract wrist origin coordinates (2.38, 4.76) during landmark normalization</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #239</t>
+          <t>Subtract wrist origin coordinates (2.39, 4.78) during landmark normalization</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Wrist landmark origin translation #240</t>
+          <t>Subtract wrist origin coordinates (2.4, 4.8) during landmark normalization</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Wrist raw pos: (2.40, 4.80) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
+          <t>Wrist raw pos: (2.4, 4.8) -&gt; Normalized wrist pos: (0.0, 0.0)</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #241</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 1</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #242</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 2</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #243</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 3</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #244</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 4</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #245</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 5</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #246</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 6</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #247</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 7</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #248</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 8</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #249</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 9</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -19779,7 +19779,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #250</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 10</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -19814,7 +19814,7 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #251</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 11</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #252</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 12</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #253</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 13</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -19919,7 +19919,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #254</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 14</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -19954,7 +19954,7 @@
         </is>
       </c>
       <c r="F255" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #255</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 15</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #256</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 16</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -20024,7 +20024,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #257</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 17</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -20059,7 +20059,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #258</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 18</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -20094,7 +20094,7 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #259</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 19</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -20150,7 +20150,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #260</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 20</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #261</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 21</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #262</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 22</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -20234,7 +20234,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #263</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 23</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -20269,7 +20269,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #264</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 24</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #265</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 25</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -20339,7 +20339,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #266</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 26</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -20374,7 +20374,7 @@
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #267</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 27</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -20409,7 +20409,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #268</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 28</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #269</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 29</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -20479,7 +20479,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #270</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 30</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #271</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 31</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #272</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 32</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -20584,7 +20584,7 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #273</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 33</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #274</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 34</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -20654,7 +20654,7 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #275</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 35</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #276</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 36</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #277</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 37</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #278</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 38</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -20815,7 +20815,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #279</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 39</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #280</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 40</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #281</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 41</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -20899,7 +20899,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #282</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 42</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #283</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 43</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #284</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 44</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -21025,7 +21025,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #285</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 45</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #286</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 46</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #287</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 47</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -21130,7 +21130,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #288</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 48</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -21144,7 +21144,7 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #289</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 49</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #290</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 50</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -21214,7 +21214,7 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #291</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 51</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -21249,7 +21249,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #292</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 52</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -21305,7 +21305,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #293</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 53</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #294</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 54</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -21354,7 +21354,7 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #295</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 55</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #296</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 56</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -21445,7 +21445,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #297</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 57</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #298</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 58</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #299</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 59</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>ISL target alphabet vocabulary mapping #300</t>
+          <t>Verify ISL target sign vocabulary mapping for target class 60</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -21564,7 +21564,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
